--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487551_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487551_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0945</v>
+        <v>4.8514</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9878</v>
+        <v>4.3971</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1068</v>
+        <v>0.4543</v>
       </c>
       <c r="G2" t="n">
         <v>7.9565</v>
@@ -610,13 +610,13 @@
         <v>2.3502</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4957</v>
+        <v>-0.7388</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9922</v>
+        <v>-0.5828</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5034999999999999</v>
+        <v>-0.156</v>
       </c>
       <c r="V2" t="n">
         <v>1.159</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. BELLO CASTRO</t>
+          <t>J. RODRIGUEZ BUCETA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3639</v>
+        <v>3.706</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3308</v>
+        <v>5.4624</v>
       </c>
       <c r="F3" t="n">
-        <v>1.033</v>
+        <v>-1.7564</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3582</v>
+        <v>5.1466</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9996</v>
+        <v>5.0198</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3585</v>
+        <v>0.1268</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8853</v>
+        <v>5.1217</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2694</v>
+        <v>4.8792</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6159</v>
+        <v>0.2425</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5271</v>
+        <v>0.0249</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2698</v>
+        <v>0.1406</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2573</v>
+        <v>-0.1157</v>
       </c>
       <c r="P3" t="n">
         <v>1.3709</v>
@@ -688,28 +688,28 @@
         <v>1.3709</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4804</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7722</v>
+        <v>-0.21</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2918</v>
+        <v>-0.4437</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1152</v>
+        <v>-2.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2178</v>
+        <v>0.5507</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1026</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BUCETA</t>
+          <t>M. BELLO CASTRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2386</v>
+        <v>3.4883</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1554</v>
+        <v>2.5355</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9168</v>
+        <v>0.9528</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1466</v>
+        <v>2.3582</v>
       </c>
       <c r="H4" t="n">
-        <v>5.0198</v>
+        <v>1.9996</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1268</v>
+        <v>0.3585</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1217</v>
+        <v>2.8853</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8792</v>
+        <v>2.2694</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2425</v>
+        <v>0.6159</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0249</v>
+        <v>-0.5271</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1406</v>
+        <v>-0.2698</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1157</v>
+        <v>-0.2573</v>
       </c>
       <c r="P4" t="n">
         <v>1.3709</v>
@@ -766,22 +766,22 @@
         <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1211</v>
+        <v>-0.356</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.517</v>
+        <v>-0.5676</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6041</v>
+        <v>0.2116</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.1578</v>
+        <v>0.1152</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5507</v>
+        <v>0.2178</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.7086</v>
+        <v>-0.1026</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8255</v>
+        <v>1.008</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7987</v>
+        <v>1.901</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-0.8931</v>
       </c>
       <c r="G5" t="n">
         <v>1.0096</v>
@@ -844,13 +844,13 @@
         <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3592</v>
+        <v>-1.1767</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.891</v>
+        <v>-0.7887</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4682</v>
+        <v>-0.388</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MONTEAGUDO FERNANDEZ</t>
+          <t>P. SABUGUEIRO ABEIJÓN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.721</v>
+        <v>0.5877</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4211</v>
+        <v>-0.0398</v>
       </c>
       <c r="F6" t="n">
-        <v>2.142</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.9067</v>
+        <v>2.6167</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6887</v>
+        <v>0.3835</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.218</v>
+        <v>2.2332</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.84</v>
+        <v>2.3939</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1258</v>
+        <v>-0.2331</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9659</v>
+        <v>2.627</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0667</v>
+        <v>0.2228</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8145</v>
+        <v>0.6166</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2521</v>
+        <v>-0.3938</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1751</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1751</v>
+        <v>0.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5701000000000001</v>
+        <v>-0.854</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1317</v>
+        <v>-0.4752</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7018</v>
+        <v>-0.3788</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8825</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.3318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7007</v>
+        <v>0.3577</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0861</v>
+        <v>-0.0162</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6145</v>
+        <v>0.374</v>
       </c>
       <c r="G7" t="n">
         <v>1.1303</v>
@@ -1000,13 +1000,13 @@
         <v>2.546</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1716</v>
+        <v>-0.5145</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7852</v>
+        <v>-0.8875</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6136</v>
+        <v>0.373</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8249</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. SABUGUEIRO ABEIJÓN</t>
+          <t>A. MONTEAGUDO FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6946</v>
+        <v>0.1734</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0398</v>
+        <v>-1.7281</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7344000000000001</v>
+        <v>1.9015</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6167</v>
+        <v>-2.9067</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3835</v>
+        <v>-0.6887</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2332</v>
+        <v>-2.218</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3939</v>
+        <v>-1.84</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2331</v>
+        <v>0.1258</v>
       </c>
       <c r="L8" t="n">
-        <v>2.627</v>
+        <v>-1.9659</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2228</v>
+        <v>-1.0667</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6166</v>
+        <v>-0.8145</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3938</v>
+        <v>-0.2521</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1751</v>
+        <v>1.1751</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7834</v>
+        <v>1.1751</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.747</v>
+        <v>0.0225</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4752</v>
+        <v>-0.4388</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2718</v>
+        <v>0.4613</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.8825</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5507</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.3318</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1352</v>
+        <v>-0.1619</v>
       </c>
       <c r="E9" t="n">
         <v>0.6689000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8041</v>
+        <v>-0.8308</v>
       </c>
       <c r="G9" t="n">
         <v>0.1314</v>
@@ -1156,13 +1156,13 @@
         <v>0.1958</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4624</v>
+        <v>-0.4892</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0594</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.403</v>
+        <v>-0.4298</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3285</v>
+        <v>-1.0879</v>
       </c>
       <c r="E10" t="n">
         <v>1.3773</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7058</v>
+        <v>-2.4652</v>
       </c>
       <c r="G10" t="n">
         <v>0.9671999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>0.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1159</v>
+        <v>-0.8753</v>
       </c>
       <c r="T10" t="n">
         <v>-0.594</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5219</v>
+        <v>-0.2813</v>
       </c>
       <c r="V10" t="n">
         <v>-1.7673</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. CASTAÑO RUBIANES</t>
+          <t>A. RODRIGUEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4409</v>
+        <v>-2.5289</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9775</v>
+        <v>-1.6376</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4634</v>
+        <v>-0.8913</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1224</v>
+        <v>-0.1638</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9251</v>
+        <v>0.6897</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1973</v>
+        <v>-0.8535</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8401</v>
+        <v>0.2237</v>
       </c>
       <c r="K11" t="n">
-        <v>1.6688</v>
+        <v>0.1429</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1713</v>
+        <v>0.0808</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7177</v>
+        <v>-0.3875</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7437</v>
+        <v>0.5468</v>
       </c>
       <c r="O11" t="n">
-        <v>0.026</v>
+        <v>-0.9344</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.546</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.917</v>
+        <v>-1.9585</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3709</v>
+        <v>0.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8077</v>
+        <v>-0.2488</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4911</v>
+        <v>-0.1782</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3166</v>
+        <v>-0.0706</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8249</v>
+        <v>-0.9412</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6083</v>
+        <v>0.2754</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4332</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ FERNANDEZ</t>
+          <t>O. CASTAÑO RUBIANES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6358</v>
+        <v>-3.2955</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6376</v>
+        <v>-1.5915</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9982</v>
+        <v>-1.704</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1638</v>
+        <v>1.1224</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6897</v>
+        <v>0.9251</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8535</v>
+        <v>0.1973</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2237</v>
+        <v>1.8401</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1429</v>
+        <v>1.6688</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0808</v>
+        <v>0.1713</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3875</v>
+        <v>-0.7177</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5468</v>
+        <v>-0.7437</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9344</v>
+        <v>0.026</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1751</v>
+        <v>-2.546</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7834</v>
+        <v>1.3709</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3557</v>
+        <v>-0.0469</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1782</v>
+        <v>-0.1229</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1775</v>
+        <v>0.076</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9412</v>
+        <v>-1.8249</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2754</v>
+        <v>0.6083</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2166</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.098400000000002</v>
+        <v>7.0983</v>
       </c>
       <c r="E13" t="n">
         <v>11.329</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.2309</v>
+        <v>-4.2307</v>
       </c>
       <c r="G13" t="n">
         <v>19.3684</v>
@@ -1468,13 +1468,13 @@
         <v>13.7092</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.9312</v>
+        <v>-5.931400000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.905</v>
+        <v>-4.9051</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0262</v>
+        <v>-1.0263</v>
       </c>
       <c r="V13" t="n">
         <v>-5.359400000000001</v>
@@ -1483,13 +1483,13 @@
         <v>3.304399999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.6639</v>
+        <v>-8.663899999999998</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>R. PEREZ MARTIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7554</v>
+        <v>2.0442</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4973</v>
+        <v>3.5075</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7419</v>
+        <v>-1.4633</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.801</v>
+        <v>-1.6906</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4428</v>
+        <v>-0.2204</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3582</v>
+        <v>-1.4701</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5072</v>
+        <v>1.9478</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3455</v>
+        <v>1.8169</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1617</v>
+        <v>0.1309</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.3082</v>
+        <v>-3.6384</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.7883</v>
+        <v>-2.0373</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5198</v>
+        <v>-1.601</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1751</v>
+        <v>1.9585</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1543</v>
+        <v>1.9585</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6128</v>
+        <v>0.2267</v>
       </c>
       <c r="T14" t="n">
-        <v>3.0418</v>
+        <v>-0.2076</v>
       </c>
       <c r="U14" t="n">
-        <v>0.571</v>
+        <v>0.4343</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7685</v>
+        <v>1.5495</v>
       </c>
       <c r="W14" t="n">
-        <v>1.9275</v>
+        <v>1.7673</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.159</v>
+        <v>-0.2178</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. PEREZ MARTIN</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.752</v>
+        <v>1.8406</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4052</v>
+        <v>3.5529</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6532</v>
+        <v>-1.7123</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.6906</v>
+        <v>-1.801</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2204</v>
+        <v>-1.4428</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4701</v>
+        <v>-0.3582</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9478</v>
+        <v>1.5072</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8169</v>
+        <v>1.3455</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1309</v>
+        <v>0.1617</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.6384</v>
+        <v>-3.3082</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.0373</v>
+        <v>-2.7883</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.601</v>
+        <v>-0.5198</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9585</v>
+        <v>1.1751</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9585</v>
+        <v>2.1543</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0655</v>
+        <v>1.6979</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.31</v>
+        <v>1.0975</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2444</v>
+        <v>0.6005</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5495</v>
+        <v>0.7685</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7673</v>
+        <v>1.9275</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2178</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. CABAÑEROS MORALA</t>
+          <t>Y. IGLESIAS MENDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0271</v>
+        <v>0.3725</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.2488</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7203000000000001</v>
+        <v>0.1237</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.4453</v>
+        <v>-4.2835</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.7946</v>
+        <v>-0.5597</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3493</v>
+        <v>-3.7237</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8587</v>
+        <v>-1.593</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6874</v>
+        <v>0.9339</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5462</v>
+        <v>-2.5269</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.304</v>
+        <v>-2.6905</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.1071</v>
+        <v>-1.4936</v>
       </c>
       <c r="O16" t="n">
         <v>-1.1969</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1751</v>
+        <v>1.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7626</v>
+        <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>0.765</v>
+        <v>0.5546</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6099</v>
+        <v>-0.1053</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1552</v>
+        <v>0.6599</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8825</v>
+        <v>2.9263</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2166</v>
+        <v>2.9263</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y. IGLESIAS MENDEZ</t>
+          <t>P. CABAÑEROS MORALA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0755</v>
+        <v>0.2216</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0442</v>
+        <v>0.6451</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1197</v>
+        <v>-0.4235</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.2835</v>
+        <v>-1.4453</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5597</v>
+        <v>-2.7946</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.7237</v>
+        <v>1.3493</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.593</v>
+        <v>1.8587</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9339</v>
+        <v>-0.6874</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.5269</v>
+        <v>2.5462</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6905</v>
+        <v>-3.304</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4936</v>
+        <v>-2.1071</v>
       </c>
       <c r="O17" t="n">
         <v>-1.1969</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1751</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1543</v>
+        <v>1.7626</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1066</v>
+        <v>0.9595</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.31</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4165</v>
+        <v>0.452</v>
       </c>
       <c r="V17" t="n">
-        <v>2.9263</v>
+        <v>1.8825</v>
       </c>
       <c r="W17" t="n">
-        <v>2.9263</v>
+        <v>1.2166</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6304</v>
+        <v>-0.4479</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.336</v>
+        <v>-0.2337</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2944</v>
+        <v>-0.2142</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5233</v>
@@ -1858,13 +1858,13 @@
         <v>0.1958</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3029</v>
+        <v>-0.1204</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3564</v>
+        <v>-0.2541</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0535</v>
+        <v>0.1337</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. SALVADORES ALVAREZ</t>
+          <t>M. GONZALEZ BLAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.5324</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2093</v>
+        <v>0.2503</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9436</v>
+        <v>-0.7826</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2128</v>
+        <v>-1.9463</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5254</v>
+        <v>-1.8751</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6874</v>
+        <v>-0.0712</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8839</v>
+        <v>0.7484</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6975</v>
+        <v>0.1633</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1865</v>
+        <v>0.5851</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.0968</v>
+        <v>-2.6947</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2228</v>
+        <v>-2.0384</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8739</v>
+        <v>-0.6563</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7626</v>
+        <v>1.5668</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2998</v>
+        <v>-0.1529</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0465</v>
+        <v>-0.4982</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2534</v>
+        <v>0.3452</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9412</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SAN MILLAN GONZALEZ-QUEVEDO</t>
+          <t>F. SALVADORES ALVAREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7945</v>
+        <v>-0.5702</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0592</v>
+        <v>0.721</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2647</v>
+        <v>-1.2911</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3837</v>
+        <v>-1.2128</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1872</v>
+        <v>-0.5254</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8035</v>
+        <v>-0.6874</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0225</v>
+        <v>1.8839</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0987</v>
+        <v>0.6975</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1212</v>
+        <v>1.1865</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4062</v>
+        <v>-3.0968</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0885</v>
+        <v>-1.2228</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6822</v>
+        <v>-1.8739</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3917</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3917</v>
+        <v>1.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1366</v>
+        <v>1.464</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4158</v>
+        <v>0.5581</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2792</v>
+        <v>0.9059</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6659</v>
+        <v>0.9412</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6659</v>
+        <v>1.2166</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. NONGO N'SALA</t>
+          <t>M. SAN MILLAN GONZALEZ-QUEVEDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7991</v>
+        <v>-0.7189</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3954</v>
+        <v>-0.9569</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4037</v>
+        <v>0.2379</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6504</v>
+        <v>-0.3837</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2514</v>
+        <v>-1.1872</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.399</v>
+        <v>0.8035</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0204</v>
+        <v>0.0225</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0204</v>
+        <v>-0.0987</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.1212</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6708</v>
+        <v>-0.4062</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2719</v>
+        <v>-1.0885</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.399</v>
+        <v>0.6822</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7834</v>
+        <v>0.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6347</v>
+        <v>-0.061</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5634</v>
+        <v>-0.3135</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0713</v>
+        <v>0.2525</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. DOMINGUEZ ITURZA</t>
+          <t>A. NONGO N'SALA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0198</v>
+        <v>-0.8968</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8505</v>
+        <v>-0.6001</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8703</v>
+        <v>-0.2968</v>
       </c>
       <c r="G22" t="n">
-        <v>1.8104</v>
+        <v>-0.6504</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7758</v>
+        <v>-0.2514</v>
       </c>
       <c r="I22" t="n">
-        <v>2.5862</v>
+        <v>-0.399</v>
       </c>
       <c r="J22" t="n">
-        <v>4.8999</v>
+        <v>0.0204</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7179</v>
+        <v>0.0204</v>
       </c>
       <c r="L22" t="n">
-        <v>4.182</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.0895</v>
+        <v>-0.6708</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4936</v>
+        <v>-0.2719</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5958</v>
+        <v>-0.399</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5668</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3709</v>
+        <v>0.1958</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8369</v>
+        <v>0.537</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.387</v>
+        <v>0.3588</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2239</v>
+        <v>0.1782</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1003</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3756</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. GONZALEZ BLAS</t>
+          <t>M. DOMINGUEZ ITURZA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1805</v>
+        <v>-0.8999</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2614</v>
+        <v>2.1575</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9191</v>
+        <v>-3.0574</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9463</v>
+        <v>1.8104</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8751</v>
+        <v>-0.7758</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0712</v>
+        <v>2.5862</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7484</v>
+        <v>4.8999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1633</v>
+        <v>0.7179</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5851</v>
+        <v>4.182</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.6947</v>
+        <v>-3.0895</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.0384</v>
+        <v>-1.4936</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6563</v>
+        <v>-1.5958</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5668</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5668</v>
+        <v>1.3709</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.801</v>
+        <v>0.9567</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0098</v>
+        <v>-0.08</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2088</v>
+        <v>1.0367</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.1003</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.3756</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.3987</v>
+        <v>-6.829</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4711</v>
+        <v>-5.0618</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9276</v>
+        <v>-1.7672</v>
       </c>
       <c r="G24" t="n">
         <v>-7.2421</v>
@@ -2326,13 +2326,13 @@
         <v>1.7626</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0184</v>
+        <v>0.5514</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4464</v>
+        <v>-0.0371</v>
       </c>
       <c r="U24" t="n">
-        <v>0.428</v>
+        <v>0.5884</v>
       </c>
       <c r="V24" t="n">
         <v>0.0576</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.098400000000001</v>
+        <v>-6.4162</v>
       </c>
       <c r="E25" t="n">
-        <v>4.2309</v>
+        <v>4.230600000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.3291</v>
+        <v>-10.6468</v>
       </c>
       <c r="G25" t="n">
         <v>-19.3686</v>
@@ -2374,7 +2374,7 @@
         <v>-13.9625</v>
       </c>
       <c r="I25" t="n">
-        <v>-5.4059</v>
+        <v>-5.405900000000001</v>
       </c>
       <c r="J25" t="n">
         <v>8.249999999999998</v>
@@ -2395,7 +2395,7 @@
         <v>-10.6303</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9793000000000001</v>
+        <v>0.9792999999999998</v>
       </c>
       <c r="Q25" t="n">
         <v>-13.7092</v>
@@ -2404,13 +2404,13 @@
         <v>14.6884</v>
       </c>
       <c r="S25" t="n">
-        <v>5.9314</v>
+        <v>6.6135</v>
       </c>
       <c r="T25" t="n">
         <v>1.0262</v>
       </c>
       <c r="U25" t="n">
-        <v>4.9052</v>
+        <v>5.5873</v>
       </c>
       <c r="V25" t="n">
         <v>5.359399999999999</v>
